--- a/output/科研训练计划_2025-2026-2/05_课程目标结果表.xlsx
+++ b/output/科研训练计划_2025-2026-2/05_课程目标结果表.xlsx
@@ -698,7 +698,7 @@
         <v>0.7607859285714286</v>
       </c>
       <c r="V2" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>0.8503645</v>
       </c>
       <c r="V3" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
@@ -966,7 +966,7 @@
         <v>0.8395042142857142</v>
       </c>
       <c r="V4" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
@@ -1100,7 +1100,7 @@
         <v>0.8082787857142856</v>
       </c>
       <c r="V5" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
@@ -1234,7 +1234,7 @@
         <v>0.808997857142857</v>
       </c>
       <c r="V6" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
@@ -1368,7 +1368,7 @@
         <v>0.729428357142857</v>
       </c>
       <c r="V7" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
@@ -1502,7 +1502,7 @@
         <v>0.8371499999999999</v>
       </c>
       <c r="V8" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
@@ -1636,7 +1636,7 @@
         <v>0.8653477142857142</v>
       </c>
       <c r="V9" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
@@ -1770,7 +1770,7 @@
         <v>0.8424285714285713</v>
       </c>
       <c r="V10" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
@@ -1904,7 +1904,7 @@
         <v>0.8496357142857142</v>
       </c>
       <c r="V11" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
@@ -2038,11 +2038,11 @@
         <v>0.6992071428571428</v>
       </c>
       <c r="V12" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>未达标</t>
+          <t>达标</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -2172,7 +2172,7 @@
         <v>0.8222271428571428</v>
       </c>
       <c r="V13" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
@@ -2306,7 +2306,7 @@
         <v>0.8265069285714285</v>
       </c>
       <c r="V14" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
@@ -2440,7 +2440,7 @@
         <v>0.8204047142857142</v>
       </c>
       <c r="V15" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
@@ -2574,7 +2574,7 @@
         <v>0.811792357142857</v>
       </c>
       <c r="V16" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
@@ -2708,7 +2708,7 @@
         <v>0.881986</v>
       </c>
       <c r="V17" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
@@ -2842,7 +2842,7 @@
         <v>0.8780742142857141</v>
       </c>
       <c r="V18" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
@@ -2976,7 +2976,7 @@
         <v>0.8517785714285713</v>
       </c>
       <c r="V19" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
@@ -3110,7 +3110,7 @@
         <v>0.8726852142857141</v>
       </c>
       <c r="V20" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
@@ -3244,7 +3244,7 @@
         <v>0.8261497857142857</v>
       </c>
       <c r="V21" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
@@ -3378,7 +3378,7 @@
         <v>0.8754359285714285</v>
       </c>
       <c r="V22" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
@@ -3512,7 +3512,7 @@
         <v>0.8399777857142856</v>
       </c>
       <c r="V23" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W23" t="inlineStr">
         <is>
@@ -3646,7 +3646,7 @@
         <v>0.7759354999999999</v>
       </c>
       <c r="V24" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W24" t="inlineStr">
         <is>
@@ -3780,7 +3780,7 @@
         <v>0.8235640714285714</v>
       </c>
       <c r="V25" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W25" t="inlineStr">
         <is>
@@ -3914,7 +3914,7 @@
         <v>0.8662787857142856</v>
       </c>
       <c r="V26" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W26" t="inlineStr">
         <is>
@@ -4048,7 +4048,7 @@
         <v>0.8640644999999999</v>
       </c>
       <c r="V27" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W27" t="inlineStr">
         <is>
@@ -4182,7 +4182,7 @@
         <v>0.8340075714285713</v>
       </c>
       <c r="V28" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W28" t="inlineStr">
         <is>
@@ -4316,7 +4316,7 @@
         <v>0.8698702857142856</v>
       </c>
       <c r="V29" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W29" t="inlineStr">
         <is>
@@ -4450,7 +4450,7 @@
         <v>0.8074359285714284</v>
       </c>
       <c r="V30" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W30" t="inlineStr">
         <is>
@@ -4584,7 +4584,7 @@
         <v>0.8560009285714284</v>
       </c>
       <c r="V31" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W31" t="inlineStr">
         <is>
@@ -4718,7 +4718,7 @@
         <v>0.8802216428571427</v>
       </c>
       <c r="V32" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W32" t="inlineStr">
         <is>
@@ -4852,7 +4852,7 @@
         <v>0.863298857142857</v>
       </c>
       <c r="V33" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W33" t="inlineStr">
         <is>
@@ -4986,7 +4986,7 @@
         <v>0.8177926428571428</v>
       </c>
       <c r="V34" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W34" t="inlineStr">
         <is>
@@ -5120,7 +5120,7 @@
         <v>0.8650813571428569</v>
       </c>
       <c r="V35" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W35" t="inlineStr">
         <is>
@@ -5254,7 +5254,7 @@
         <v>0.8795640714285713</v>
       </c>
       <c r="V36" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W36" t="inlineStr">
         <is>
@@ -5388,7 +5388,7 @@
         <v>0.7349214285714286</v>
       </c>
       <c r="V37" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W37" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
         <v>0.8344285714285714</v>
       </c>
       <c r="V38" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W38" t="inlineStr">
         <is>
@@ -5656,7 +5656,7 @@
         <v>0.860992857142857</v>
       </c>
       <c r="V39" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W39" t="inlineStr">
         <is>
@@ -5790,7 +5790,7 @@
         <v>0.7607787857142857</v>
       </c>
       <c r="V40" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W40" t="inlineStr">
         <is>
@@ -5924,7 +5924,7 @@
         <v>0.8591502142857141</v>
       </c>
       <c r="V41" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W41" t="inlineStr">
         <is>
@@ -6058,7 +6058,7 @@
         <v>0.8580002142857143</v>
       </c>
       <c r="V42" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W42" t="inlineStr">
         <is>
@@ -6192,7 +6192,7 @@
         <v>0.8414212142857143</v>
       </c>
       <c r="V43" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W43" t="inlineStr">
         <is>
@@ -6326,7 +6326,7 @@
         <v>0.8820002142857142</v>
       </c>
       <c r="V44" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W44" t="inlineStr">
         <is>
@@ -6460,7 +6460,7 @@
         <v>0.7112142857142856</v>
       </c>
       <c r="V45" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W45" t="inlineStr">
         <is>
@@ -6594,7 +6594,7 @@
         <v>0.8152785714285713</v>
       </c>
       <c r="V46" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W46" t="inlineStr">
         <is>
@@ -6728,7 +6728,7 @@
         <v>0.8443642857142856</v>
       </c>
       <c r="V47" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W47" t="inlineStr">
         <is>
@@ -6862,7 +6862,7 @@
         <v>0.8749997857142855</v>
       </c>
       <c r="V48" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W48" t="inlineStr">
         <is>
@@ -6996,7 +6996,7 @@
         <v>0.8832845714285713</v>
       </c>
       <c r="V49" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W49" t="inlineStr">
         <is>
@@ -7130,7 +7130,7 @@
         <v>0.8422216428571427</v>
       </c>
       <c r="V50" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W50" t="inlineStr">
         <is>
@@ -7264,7 +7264,7 @@
         <v>0.8835202142857141</v>
       </c>
       <c r="V51" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W51" t="inlineStr">
         <is>
@@ -7398,7 +7398,7 @@
         <v>0.9003059285714284</v>
       </c>
       <c r="V52" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W52" t="inlineStr">
         <is>
@@ -7532,7 +7532,7 @@
         <v>0.8980785714285714</v>
       </c>
       <c r="V53" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W53" t="inlineStr">
         <is>
@@ -7666,7 +7666,7 @@
         <v>0.8845002857142856</v>
       </c>
       <c r="V54" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W54" t="inlineStr">
         <is>
@@ -7800,7 +7800,7 @@
         <v>0.8382147142857143</v>
       </c>
       <c r="V55" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W55" t="inlineStr">
         <is>
@@ -7934,7 +7934,7 @@
         <v>0.8370642857142856</v>
       </c>
       <c r="V56" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W56" t="inlineStr">
         <is>
@@ -8068,7 +8068,7 @@
         <v>0.8341357142857142</v>
       </c>
       <c r="V57" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W57" t="inlineStr">
         <is>
@@ -8202,7 +8202,7 @@
         <v>0.8191354999999999</v>
       </c>
       <c r="V58" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W58" t="inlineStr">
         <is>
@@ -8336,7 +8336,7 @@
         <v>0.864357357142857</v>
       </c>
       <c r="V59" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W59" t="inlineStr">
         <is>
@@ -8470,7 +8470,7 @@
         <v>0.8549287857142857</v>
       </c>
       <c r="V60" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W60" t="inlineStr">
         <is>
@@ -8604,7 +8604,7 @@
         <v>0.879207357142857</v>
       </c>
       <c r="V61" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W61" t="inlineStr">
         <is>
@@ -8738,7 +8738,7 @@
         <v>0.8336117142857141</v>
       </c>
       <c r="V62" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W62" t="inlineStr">
         <is>
@@ -8872,7 +8872,7 @@
         <v>0.7669287857142857</v>
       </c>
       <c r="V63" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W63" t="inlineStr">
         <is>
@@ -9006,7 +9006,7 @@
         <v>0.8697930714285713</v>
       </c>
       <c r="V64" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W64" t="inlineStr">
         <is>
@@ -9140,7 +9140,7 @@
         <v>0.8713559999999998</v>
       </c>
       <c r="V65" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W65" t="inlineStr">
         <is>
@@ -9274,7 +9274,7 @@
         <v>0.8895273571428569</v>
       </c>
       <c r="V66" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W66" t="inlineStr">
         <is>
@@ -9408,7 +9408,7 @@
         <v>0.8182212142857143</v>
       </c>
       <c r="V67" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W67" t="inlineStr">
         <is>
@@ -9542,7 +9542,7 @@
         <v>0.8706359285714285</v>
       </c>
       <c r="V68" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W68" t="inlineStr">
         <is>
@@ -9676,7 +9676,7 @@
         <v>0.8612785714285713</v>
       </c>
       <c r="V69" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W69" t="inlineStr">
         <is>
@@ -9810,7 +9810,7 @@
         <v>0.8144926428571428</v>
       </c>
       <c r="V70" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W70" t="inlineStr">
         <is>
@@ -9944,7 +9944,7 @@
         <v>0.8703644999999999</v>
       </c>
       <c r="V71" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W71" t="inlineStr">
         <is>
@@ -10078,7 +10078,7 @@
         <v>0.8637192142857142</v>
       </c>
       <c r="V72" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W72" t="inlineStr">
         <is>
@@ -10212,7 +10212,7 @@
         <v>0.8207271428571428</v>
       </c>
       <c r="V73" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W73" t="inlineStr">
         <is>
@@ -10346,7 +10346,7 @@
         <v>0.7056499999999999</v>
       </c>
       <c r="V74" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W74" t="inlineStr">
         <is>
@@ -10480,7 +10480,7 @@
         <v>0.7007142857142856</v>
       </c>
       <c r="V75" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W75" t="inlineStr">
         <is>
@@ -10614,7 +10614,7 @@
         <v>0.8411249999999998</v>
       </c>
       <c r="V76" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W76" t="inlineStr">
         <is>
@@ -10748,7 +10748,7 @@
         <v>0.8238057142857143</v>
       </c>
       <c r="V77" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W77" t="inlineStr">
         <is>
@@ -10882,7 +10882,7 @@
         <v>0.8254997857142856</v>
       </c>
       <c r="V78" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W78" t="inlineStr">
         <is>
@@ -11016,7 +11016,7 @@
         <v>0.8949283571428569</v>
       </c>
       <c r="V79" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W79" t="inlineStr">
         <is>
@@ -11150,7 +11150,7 @@
         <v>0.8357142857142856</v>
       </c>
       <c r="V80" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W80" t="inlineStr">
         <is>
@@ -11284,7 +11284,7 @@
         <v>0.870357357142857</v>
       </c>
       <c r="V81" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W81" t="inlineStr">
         <is>
@@ -11418,7 +11418,7 @@
         <v>0.747</v>
       </c>
       <c r="V82" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W82" t="inlineStr">
         <is>
@@ -11552,7 +11552,7 @@
         <v>0.7796666666666666</v>
       </c>
       <c r="V83" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W83" t="inlineStr">
         <is>
@@ -11686,7 +11686,7 @@
         <v>0.7988098333333332</v>
       </c>
       <c r="V84" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W84" t="inlineStr">
         <is>
@@ -11820,7 +11820,7 @@
         <v>0.9171666666666666</v>
       </c>
       <c r="V85" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W85" t="inlineStr">
         <is>
@@ -11954,7 +11954,7 @@
         <v>0.7900335000000001</v>
       </c>
       <c r="V86" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W86" t="inlineStr">
         <is>
@@ -12088,7 +12088,7 @@
         <v>0.7521666666666668</v>
       </c>
       <c r="V87" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W87" t="inlineStr">
         <is>
@@ -12222,7 +12222,7 @@
         <v>0.793</v>
       </c>
       <c r="V88" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W88" t="inlineStr">
         <is>
@@ -12356,7 +12356,7 @@
         <v>0.9151916666666667</v>
       </c>
       <c r="V89" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W89" t="inlineStr">
         <is>
@@ -12490,7 +12490,7 @@
         <v>0.8888333333333334</v>
       </c>
       <c r="V90" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W90" t="inlineStr">
         <is>
@@ -12624,7 +12624,7 @@
         <v>0.9129999999999999</v>
       </c>
       <c r="V91" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W91" t="inlineStr">
         <is>
@@ -12758,7 +12758,7 @@
         <v>0.7376666666666667</v>
       </c>
       <c r="V92" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W92" t="inlineStr">
         <is>
@@ -12892,7 +12892,7 @@
         <v>0.8075786666666668</v>
       </c>
       <c r="V93" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W93" t="inlineStr">
         <is>
@@ -13026,7 +13026,7 @@
         <v>0.7556666666666667</v>
       </c>
       <c r="V94" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W94" t="inlineStr">
         <is>
@@ -13160,7 +13160,7 @@
         <v>0.7821585000000001</v>
       </c>
       <c r="V95" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W95" t="inlineStr">
         <is>
@@ -13294,7 +13294,7 @@
         <v>0.8227258333333334</v>
       </c>
       <c r="V96" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W96" t="inlineStr">
         <is>
@@ -13428,7 +13428,7 @@
         <v>0.8844413333333333</v>
       </c>
       <c r="V97" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W97" t="inlineStr">
         <is>
@@ -13562,7 +13562,7 @@
         <v>0.8689535</v>
       </c>
       <c r="V98" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W98" t="inlineStr">
         <is>
@@ -13696,7 +13696,7 @@
         <v>0.8005000000000001</v>
       </c>
       <c r="V99" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W99" t="inlineStr">
         <is>
@@ -13830,7 +13830,7 @@
         <v>0.8372313333333333</v>
       </c>
       <c r="V100" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W100" t="inlineStr">
         <is>
@@ -13964,7 +13964,7 @@
         <v>0.7778333333333334</v>
       </c>
       <c r="V101" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W101" t="inlineStr">
         <is>
@@ -14098,7 +14098,7 @@
         <v>0.9551666666666667</v>
       </c>
       <c r="V102" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W102" t="inlineStr">
         <is>
@@ -14232,7 +14232,7 @@
         <v>0.7942961666666667</v>
       </c>
       <c r="V103" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W103" t="inlineStr">
         <is>
@@ -14366,7 +14366,7 @@
         <v>0.7626666666666666</v>
       </c>
       <c r="V104" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W104" t="inlineStr">
         <is>
@@ -14500,7 +14500,7 @@
         <v>0.7791666666666667</v>
       </c>
       <c r="V105" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W105" t="inlineStr">
         <is>
@@ -14634,7 +14634,7 @@
         <v>0.8205000000000001</v>
       </c>
       <c r="V106" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W106" t="inlineStr">
         <is>
@@ -14768,7 +14768,7 @@
         <v>0.8225000000000001</v>
       </c>
       <c r="V107" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W107" t="inlineStr">
         <is>
@@ -14902,7 +14902,7 @@
         <v>0.8119785</v>
       </c>
       <c r="V108" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W108" t="inlineStr">
         <is>
@@ -15036,7 +15036,7 @@
         <v>0.8896010000000001</v>
       </c>
       <c r="V109" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W109" t="inlineStr">
         <is>
@@ -15170,7 +15170,7 @@
         <v>0.7508333333333334</v>
       </c>
       <c r="V110" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W110" t="inlineStr">
         <is>
@@ -15304,7 +15304,7 @@
         <v>0.8862323333333334</v>
       </c>
       <c r="V111" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W111" t="inlineStr">
         <is>
@@ -15438,7 +15438,7 @@
         <v>0.9446666666666668</v>
       </c>
       <c r="V112" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W112" t="inlineStr">
         <is>
@@ -15572,7 +15572,7 @@
         <v>0.9049343333333335</v>
       </c>
       <c r="V113" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W113" t="inlineStr">
         <is>
@@ -15706,7 +15706,7 @@
         <v>0.7651666666666667</v>
       </c>
       <c r="V114" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W114" t="inlineStr">
         <is>
@@ -15840,7 +15840,7 @@
         <v>0.8866201666666669</v>
       </c>
       <c r="V115" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W115" t="inlineStr">
         <is>
@@ -15974,7 +15974,7 @@
         <v>0.8585</v>
       </c>
       <c r="V116" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W116" t="inlineStr">
         <is>
@@ -16108,7 +16108,7 @@
         <v>0.7588333333333334</v>
       </c>
       <c r="V117" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W117" t="inlineStr">
         <is>
@@ -16242,7 +16242,7 @@
         <v>0.8200000000000001</v>
       </c>
       <c r="V118" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W118" t="inlineStr">
         <is>
@@ -16376,7 +16376,7 @@
         <v>0.8445000000000001</v>
       </c>
       <c r="V119" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W119" t="inlineStr">
         <is>
@@ -16510,7 +16510,7 @@
         <v>0.7436666666666667</v>
       </c>
       <c r="V120" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W120" t="inlineStr">
         <is>
@@ -16644,7 +16644,7 @@
         <v>0.8301666666666667</v>
       </c>
       <c r="V121" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W121" t="inlineStr">
         <is>
@@ -16778,7 +16778,7 @@
         <v>0.8193333333333332</v>
       </c>
       <c r="V122" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W122" t="inlineStr">
         <is>
@@ -16912,7 +16912,7 @@
         <v>0.8686666666666667</v>
       </c>
       <c r="V123" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W123" t="inlineStr">
         <is>
@@ -17046,7 +17046,7 @@
         <v>0.9546666666666667</v>
       </c>
       <c r="V124" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W124" t="inlineStr">
         <is>
@@ -17180,7 +17180,7 @@
         <v>0.7214999999999999</v>
       </c>
       <c r="V125" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W125" t="inlineStr">
         <is>
@@ -17314,7 +17314,7 @@
         <v>0.8938333333333334</v>
       </c>
       <c r="V126" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W126" t="inlineStr">
         <is>
@@ -17448,7 +17448,7 @@
         <v>0.8145</v>
       </c>
       <c r="V127" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W127" t="inlineStr">
         <is>
@@ -17582,7 +17582,7 @@
         <v>0.876</v>
       </c>
       <c r="V128" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W128" t="inlineStr">
         <is>
@@ -17716,7 +17716,7 @@
         <v>0.8599343333333334</v>
       </c>
       <c r="V129" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W129" t="inlineStr">
         <is>
@@ -17850,7 +17850,7 @@
         <v>0.745</v>
       </c>
       <c r="V130" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W130" t="inlineStr">
         <is>
@@ -17984,7 +17984,7 @@
         <v>0.8958850000000002</v>
       </c>
       <c r="V131" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W131" t="inlineStr">
         <is>
@@ -18118,7 +18118,7 @@
         <v>0.8480516666666668</v>
       </c>
       <c r="V132" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W132" t="inlineStr">
         <is>
@@ -18252,7 +18252,7 @@
         <v>0.906</v>
       </c>
       <c r="V133" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W133" t="inlineStr">
         <is>
@@ -18386,7 +18386,7 @@
         <v>0.8874413333333333</v>
       </c>
       <c r="V134" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W134" t="inlineStr">
         <is>
@@ -18520,7 +18520,7 @@
         <v>0.8024785</v>
       </c>
       <c r="V135" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W135" t="inlineStr">
         <is>
@@ -18654,7 +18654,7 @@
         <v>0.8293333333333334</v>
       </c>
       <c r="V136" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W136" t="inlineStr">
         <is>
@@ -18788,7 +18788,7 @@
         <v>0.8266666666666667</v>
       </c>
       <c r="V137" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W137" t="inlineStr">
         <is>
@@ -18922,7 +18922,7 @@
         <v>0.7738333333333334</v>
       </c>
       <c r="V138" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W138" t="inlineStr">
         <is>
@@ -19056,7 +19056,7 @@
         <v>0.8200000000000001</v>
       </c>
       <c r="V139" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W139" t="inlineStr">
         <is>
@@ -19190,7 +19190,7 @@
         <v>0.8341666666666666</v>
       </c>
       <c r="V140" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W140" t="inlineStr">
         <is>
@@ -19324,7 +19324,7 @@
         <v>0.9415</v>
       </c>
       <c r="V141" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W141" t="inlineStr">
         <is>
@@ -19458,7 +19458,7 @@
         <v>0.8230446666666666</v>
       </c>
       <c r="V142" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W142" t="inlineStr">
         <is>
@@ -19592,7 +19592,7 @@
         <v>0.7286666666666667</v>
       </c>
       <c r="V143" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W143" t="inlineStr">
         <is>
@@ -19726,7 +19726,7 @@
         <v>0.9626666666666667</v>
       </c>
       <c r="V144" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W144" t="inlineStr">
         <is>
@@ -19860,7 +19860,7 @@
         <v>0.8829343333333334</v>
       </c>
       <c r="V145" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W145" t="inlineStr">
         <is>
@@ -19994,7 +19994,7 @@
         <v>0.8620516666666665</v>
       </c>
       <c r="V146" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W146" t="inlineStr">
         <is>
@@ -20128,7 +20128,7 @@
         <v>0.7866666666666666</v>
       </c>
       <c r="V147" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W147" t="inlineStr">
         <is>
@@ -20262,7 +20262,7 @@
         <v>0.8928333333333333</v>
       </c>
       <c r="V148" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W148" t="inlineStr">
         <is>
@@ -20396,7 +20396,7 @@
         <v>0.9248333333333333</v>
       </c>
       <c r="V149" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W149" t="inlineStr">
         <is>
@@ -20530,7 +20530,7 @@
         <v>0.7773333333333334</v>
       </c>
       <c r="V150" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W150" t="inlineStr">
         <is>
@@ -20664,7 +20664,7 @@
         <v>0.9578333333333334</v>
       </c>
       <c r="V151" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W151" t="inlineStr">
         <is>
@@ -20798,7 +20798,7 @@
         <v>0.8204861666666667</v>
       </c>
       <c r="V152" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W152" t="inlineStr">
         <is>
@@ -20932,7 +20932,7 @@
         <v>0.8202453333333334</v>
       </c>
       <c r="V153" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W153" t="inlineStr">
         <is>
@@ -21066,7 +21066,7 @@
         <v>0.7200000000000001</v>
       </c>
       <c r="V154" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W154" t="inlineStr">
         <is>
@@ -21200,7 +21200,7 @@
         <v>0.7346666666666667</v>
       </c>
       <c r="V155" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W155" t="inlineStr">
         <is>
@@ -21334,7 +21334,7 @@
         <v>0.7645208333333334</v>
       </c>
       <c r="V156" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W156" t="inlineStr">
         <is>
@@ -21468,7 +21468,7 @@
         <v>0.8052453333333335</v>
       </c>
       <c r="V157" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W157" t="inlineStr">
         <is>
@@ -21602,7 +21602,7 @@
         <v>0.7665000000000001</v>
       </c>
       <c r="V158" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W158" t="inlineStr">
         <is>
@@ -21736,7 +21736,7 @@
         <v>0.9403333333333334</v>
       </c>
       <c r="V159" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W159" t="inlineStr">
         <is>
@@ -21870,7 +21870,7 @@
         <v>0.8190000000000001</v>
       </c>
       <c r="V160" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W160" t="inlineStr">
         <is>
@@ -22004,7 +22004,7 @@
         <v>0.9583333333333333</v>
       </c>
       <c r="V161" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W161" t="inlineStr">
         <is>
@@ -22138,7 +22138,7 @@
         <v>0.7233999999999998</v>
       </c>
       <c r="V162" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W162" t="inlineStr">
         <is>
@@ -22272,7 +22272,7 @@
         <v>0.7833999999999999</v>
       </c>
       <c r="V163" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W163" t="inlineStr">
         <is>
@@ -22406,7 +22406,7 @@
         <v>0.840797</v>
       </c>
       <c r="V164" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W164" t="inlineStr">
         <is>
@@ -22540,7 +22540,7 @@
         <v>0.8361999999999999</v>
       </c>
       <c r="V165" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W165" t="inlineStr">
         <is>
@@ -22674,7 +22674,7 @@
         <v>0.8367658</v>
       </c>
       <c r="V166" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W166" t="inlineStr">
         <is>
@@ -22808,7 +22808,7 @@
         <v>0.7049999999999998</v>
       </c>
       <c r="V167" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W167" t="inlineStr">
         <is>
@@ -22942,7 +22942,7 @@
         <v>0.8044000000000001</v>
       </c>
       <c r="V168" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W168" t="inlineStr">
         <is>
@@ -23076,7 +23076,7 @@
         <v>0.8787957999999998</v>
       </c>
       <c r="V169" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W169" t="inlineStr">
         <is>
@@ -23210,7 +23210,7 @@
         <v>0.8246</v>
       </c>
       <c r="V170" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W170" t="inlineStr">
         <is>
@@ -23344,7 +23344,7 @@
         <v>0.8254</v>
       </c>
       <c r="V171" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W171" t="inlineStr">
         <is>
@@ -23478,7 +23478,7 @@
         <v>0.707</v>
       </c>
       <c r="V172" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W172" t="inlineStr">
         <is>
@@ -23612,7 +23612,7 @@
         <v>0.8286707999999999</v>
       </c>
       <c r="V173" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W173" t="inlineStr">
         <is>
@@ -23746,7 +23746,7 @@
         <v>0.7789999999999999</v>
       </c>
       <c r="V174" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W174" t="inlineStr">
         <is>
@@ -23880,7 +23880,7 @@
         <v>0.8142559999999999</v>
       </c>
       <c r="V175" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W175" t="inlineStr">
         <is>
@@ -24014,7 +24014,7 @@
         <v>0.8397104</v>
       </c>
       <c r="V176" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W176" t="inlineStr">
         <is>
@@ -24148,7 +24148,7 @@
         <v>0.8690896</v>
       </c>
       <c r="V177" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W177" t="inlineStr">
         <is>
@@ -24282,7 +24282,7 @@
         <v>0.8486473999999999</v>
       </c>
       <c r="V178" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W178" t="inlineStr">
         <is>
@@ -24416,7 +24416,7 @@
         <v>0.8043999999999999</v>
       </c>
       <c r="V179" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W179" t="inlineStr">
         <is>
@@ -24550,7 +24550,7 @@
         <v>0.8517832</v>
       </c>
       <c r="V180" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W180" t="inlineStr">
         <is>
@@ -24684,7 +24684,7 @@
         <v>0.7533999999999998</v>
       </c>
       <c r="V181" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W181" t="inlineStr">
         <is>
@@ -24818,7 +24818,7 @@
         <v>0.8526</v>
       </c>
       <c r="V182" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W182" t="inlineStr">
         <is>
@@ -24952,7 +24952,7 @@
         <v>0.7949262000000001</v>
       </c>
       <c r="V183" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W183" t="inlineStr">
         <is>
@@ -25086,7 +25086,7 @@
         <v>0.7122000000000001</v>
       </c>
       <c r="V184" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W184" t="inlineStr">
         <is>
@@ -25220,7 +25220,7 @@
         <v>0.7589999999999999</v>
       </c>
       <c r="V185" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W185" t="inlineStr">
         <is>
@@ -25354,7 +25354,7 @@
         <v>0.8398</v>
       </c>
       <c r="V186" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W186" t="inlineStr">
         <is>
@@ -25488,7 +25488,7 @@
         <v>0.8435999999999999</v>
       </c>
       <c r="V187" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W187" t="inlineStr">
         <is>
@@ -25622,7 +25622,7 @@
         <v>0.8404245999999999</v>
       </c>
       <c r="V188" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W188" t="inlineStr">
         <is>
@@ -25756,7 +25756,7 @@
         <v>0.8468613999999999</v>
       </c>
       <c r="V189" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W189" t="inlineStr">
         <is>
@@ -25890,7 +25890,7 @@
         <v>0.7382</v>
       </c>
       <c r="V190" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W190" t="inlineStr">
         <is>
@@ -26024,7 +26024,7 @@
         <v>0.8397385999999999</v>
       </c>
       <c r="V191" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W191" t="inlineStr">
         <is>
@@ -26158,7 +26158,7 @@
         <v>0.8518</v>
       </c>
       <c r="V192" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W192" t="inlineStr">
         <is>
@@ -26292,7 +26292,7 @@
         <v>0.8468613999999999</v>
       </c>
       <c r="V193" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W193" t="inlineStr">
         <is>
@@ -26426,7 +26426,7 @@
         <v>0.7919999999999999</v>
       </c>
       <c r="V194" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W194" t="inlineStr">
         <is>
@@ -26560,7 +26560,7 @@
         <v>0.8638473999999998</v>
       </c>
       <c r="V195" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W195" t="inlineStr">
         <is>
@@ -26694,7 +26694,7 @@
         <v>0.857</v>
       </c>
       <c r="V196" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W196" t="inlineStr">
         <is>
@@ -26828,7 +26828,7 @@
         <v>0.7316</v>
       </c>
       <c r="V197" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W197" t="inlineStr">
         <is>
@@ -26962,7 +26962,7 @@
         <v>0.8296</v>
       </c>
       <c r="V198" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W198" t="inlineStr">
         <is>
@@ -27096,7 +27096,7 @@
         <v>0.7757999999999999</v>
       </c>
       <c r="V199" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W199" t="inlineStr">
         <is>
@@ -27230,7 +27230,7 @@
         <v>0.7273999999999999</v>
       </c>
       <c r="V200" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W200" t="inlineStr">
         <is>
@@ -27364,7 +27364,7 @@
         <v>0.8482000000000001</v>
       </c>
       <c r="V201" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W201" t="inlineStr">
         <is>
@@ -27498,7 +27498,7 @@
         <v>0.8643999999999998</v>
       </c>
       <c r="V202" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W202" t="inlineStr">
         <is>
@@ -27632,7 +27632,7 @@
         <v>0.8515999999999999</v>
       </c>
       <c r="V203" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W203" t="inlineStr">
         <is>
@@ -27766,7 +27766,7 @@
         <v>0.8848</v>
       </c>
       <c r="V204" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W204" t="inlineStr">
         <is>
@@ -27900,11 +27900,11 @@
         <v>0.6928000000000001</v>
       </c>
       <c r="V205" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W205" t="inlineStr">
         <is>
-          <t>未达标</t>
+          <t>达标</t>
         </is>
       </c>
       <c r="X205" t="inlineStr">
@@ -28034,7 +28034,7 @@
         <v>0.8446</v>
       </c>
       <c r="V206" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W206" t="inlineStr">
         <is>
@@ -28168,7 +28168,7 @@
         <v>0.8083999999999999</v>
       </c>
       <c r="V207" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W207" t="inlineStr">
         <is>
@@ -28302,7 +28302,7 @@
         <v>0.8488000000000001</v>
       </c>
       <c r="V208" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W208" t="inlineStr">
         <is>
@@ -28436,7 +28436,7 @@
         <v>0.8448614</v>
       </c>
       <c r="V209" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W209" t="inlineStr">
         <is>
@@ -28570,7 +28570,7 @@
         <v>0.7477999999999999</v>
       </c>
       <c r="V210" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W210" t="inlineStr">
         <is>
@@ -28704,7 +28704,7 @@
         <v>0.8510619999999999</v>
       </c>
       <c r="V211" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W211" t="inlineStr">
         <is>
@@ -28838,7 +28838,7 @@
         <v>0.8614620000000001</v>
       </c>
       <c r="V212" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W212" t="inlineStr">
         <is>
@@ -28972,7 +28972,7 @@
         <v>0.8482000000000001</v>
       </c>
       <c r="V213" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W213" t="inlineStr">
         <is>
@@ -29106,7 +29106,7 @@
         <v>0.8584896</v>
       </c>
       <c r="V214" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W214" t="inlineStr">
         <is>
@@ -29240,7 +29240,7 @@
         <v>0.8400246</v>
       </c>
       <c r="V215" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W215" t="inlineStr">
         <is>
@@ -29374,7 +29374,7 @@
         <v>0.761</v>
       </c>
       <c r="V216" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W216" t="inlineStr">
         <is>
@@ -29508,7 +29508,7 @@
         <v>0.8224</v>
       </c>
       <c r="V217" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W217" t="inlineStr">
         <is>
@@ -29642,7 +29642,7 @@
         <v>0.7777999999999998</v>
       </c>
       <c r="V218" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W218" t="inlineStr">
         <is>
@@ -29776,7 +29776,7 @@
         <v>0.8457999999999999</v>
       </c>
       <c r="V219" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W219" t="inlineStr">
         <is>
@@ -29910,7 +29910,7 @@
         <v>0.8551999999999998</v>
       </c>
       <c r="V220" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W220" t="inlineStr">
         <is>
@@ -30044,7 +30044,7 @@
         <v>0.8583999999999999</v>
       </c>
       <c r="V221" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W221" t="inlineStr">
         <is>
@@ -30178,7 +30178,7 @@
         <v>0.8282535999999999</v>
       </c>
       <c r="V222" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W222" t="inlineStr">
         <is>
@@ -30312,7 +30312,7 @@
         <v>0.7282</v>
       </c>
       <c r="V223" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W223" t="inlineStr">
         <is>
@@ -30446,7 +30446,7 @@
         <v>0.9093999999999999</v>
       </c>
       <c r="V224" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W224" t="inlineStr">
         <is>
@@ -30580,7 +30580,7 @@
         <v>0.8506614000000001</v>
       </c>
       <c r="V225" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W225" t="inlineStr">
         <is>
@@ -30714,7 +30714,7 @@
         <v>0.8748619999999999</v>
       </c>
       <c r="V226" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W226" t="inlineStr">
         <is>
@@ -30848,7 +30848,7 @@
         <v>0.7649999999999999</v>
       </c>
       <c r="V227" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W227" t="inlineStr">
         <is>
@@ -30982,7 +30982,7 @@
         <v>0.8907999999999999</v>
       </c>
       <c r="V228" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W228" t="inlineStr">
         <is>
@@ -31116,7 +31116,7 @@
         <v>0.8286</v>
       </c>
       <c r="V229" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W229" t="inlineStr">
         <is>
@@ -31250,7 +31250,7 @@
         <v>0.7865999999999999</v>
       </c>
       <c r="V230" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W230" t="inlineStr">
         <is>
@@ -31384,7 +31384,7 @@
         <v>0.8635999999999999</v>
       </c>
       <c r="V231" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W231" t="inlineStr">
         <is>
@@ -31518,7 +31518,7 @@
         <v>0.7969834</v>
       </c>
       <c r="V232" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W232" t="inlineStr">
         <is>
@@ -31652,7 +31652,7 @@
         <v>0.8176707999999999</v>
       </c>
       <c r="V233" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W233" t="inlineStr">
         <is>
@@ -31786,7 +31786,7 @@
         <v>0.7101999999999999</v>
       </c>
       <c r="V234" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W234" t="inlineStr">
         <is>
@@ -31920,7 +31920,7 @@
         <v>0.7063999999999999</v>
       </c>
       <c r="V235" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W235" t="inlineStr">
         <is>
@@ -32054,7 +32054,7 @@
         <v>0.7774249999999999</v>
       </c>
       <c r="V236" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W236" t="inlineStr">
         <is>
@@ -32188,7 +32188,7 @@
         <v>0.8270707999999999</v>
       </c>
       <c r="V237" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W237" t="inlineStr">
         <is>
@@ -32322,7 +32322,7 @@
         <v>0.7688</v>
       </c>
       <c r="V238" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W238" t="inlineStr">
         <is>
@@ -32456,7 +32456,7 @@
         <v>0.9157999999999999</v>
       </c>
       <c r="V239" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W239" t="inlineStr">
         <is>
@@ -32590,7 +32590,7 @@
         <v>0.8271999999999999</v>
       </c>
       <c r="V240" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W240" t="inlineStr">
         <is>
@@ -32724,7 +32724,7 @@
         <v>0.8629999999999999</v>
       </c>
       <c r="V241" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W241" t="inlineStr">
         <is>
@@ -32963,10 +32963,10 @@
         <v>0.8368277482142856</v>
       </c>
       <c r="N2" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="O2" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
@@ -33046,7 +33046,7 @@
         <v>0.8333325729166667</v>
       </c>
       <c r="N3" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="O3" t="n">
         <v>80</v>
@@ -33129,10 +33129,10 @@
         <v>0.8156325275</v>
       </c>
       <c r="N4" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="O4" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
